--- a/data/trans_dic/P7_R-Provincia-trans_dic.xlsx
+++ b/data/trans_dic/P7_R-Provincia-trans_dic.xlsx
@@ -527,7 +527,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población con salud general regular o mala</t>
+          <t>Población con salud general regular o mala (tasa de respuesta: 99,93%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -717,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>11,9; 20,85</t>
+          <t>12,5; 21,26</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>19,85; 30,62</t>
+          <t>19,98; 30,7</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>19,34; 29,79</t>
+          <t>19,5; 30,07</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>18,88; 29,01</t>
+          <t>19,11; 29,15</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>13,96; 23,84</t>
+          <t>13,98; 23,22</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>34,08; 46,14</t>
+          <t>33,78; 46,21</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>28,03; 39,66</t>
+          <t>28,17; 39,42</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>28,71; 38,59</t>
+          <t>28,31; 38,54</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>14,09; 20,91</t>
+          <t>14,27; 20,63</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>28,81; 36,42</t>
+          <t>28,67; 36,48</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>25,49; 32,78</t>
+          <t>25,23; 32,64</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>24,81; 31,98</t>
+          <t>24,75; 31,99</t>
         </is>
       </c>
     </row>
@@ -857,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>14,1; 21,27</t>
+          <t>14,31; 21,32</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>14,17; 21,44</t>
+          <t>14,18; 21,45</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>11,51; 18,08</t>
+          <t>11,54; 18,02</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>11,71; 19,03</t>
+          <t>11,55; 19,33</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>27,77; 36,35</t>
+          <t>28,28; 36,34</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>27,09; 35,46</t>
+          <t>27,23; 35,89</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>18,75; 26,21</t>
+          <t>18,99; 26,26</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>15,58; 21,61</t>
+          <t>15,85; 21,25</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>22,16; 27,74</t>
+          <t>22,23; 27,62</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>21,41; 27,28</t>
+          <t>21,84; 27,35</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>16,09; 21,24</t>
+          <t>16,19; 21,02</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>14,36; 19,24</t>
+          <t>14,19; 19,01</t>
         </is>
       </c>
     </row>
@@ -997,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>10,81; 18,23</t>
+          <t>11,21; 19,12</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>12,07; 20,49</t>
+          <t>12,08; 20,8</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>9,92; 16,91</t>
+          <t>9,9; 16,74</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>15,48; 23,42</t>
+          <t>15,56; 23,27</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>27,26; 37,45</t>
+          <t>28,02; 38,2</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>18,89; 28,52</t>
+          <t>19,37; 28,89</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>12,42; 21,39</t>
+          <t>12,79; 21,11</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>19,03; 26,01</t>
+          <t>18,78; 25,8</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>20,34; 27,41</t>
+          <t>20,42; 26,89</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>16,79; 23,38</t>
+          <t>16,78; 22,99</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>12,39; 17,94</t>
+          <t>12,37; 17,74</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>18,36; 23,66</t>
+          <t>18,19; 23,42</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>8,31; 15,24</t>
+          <t>8,36; 15,1</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>15,41; 24,27</t>
+          <t>16,03; 24,35</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>14,86; 23,03</t>
+          <t>14,83; 23,22</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>15,02; 25,1</t>
+          <t>14,82; 25,12</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>23,0; 31,79</t>
+          <t>22,74; 31,93</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>29,27; 38,82</t>
+          <t>29,33; 39,06</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>25,96; 35,46</t>
+          <t>26,03; 36,11</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>12,63; 27,4</t>
+          <t>12,73; 27,43</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>16,76; 22,58</t>
+          <t>16,86; 22,47</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>23,73; 30,05</t>
+          <t>23,48; 30,04</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>21,82; 28,13</t>
+          <t>21,73; 28,37</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>15,29; 24,87</t>
+          <t>14,76; 24,76</t>
         </is>
       </c>
     </row>
@@ -1277,62 +1277,62 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>15,55; 27,01</t>
+          <t>16,0; 26,7</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>11,73; 22,61</t>
+          <t>11,9; 22,52</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>15,93; 27,04</t>
+          <t>16,1; 27,78</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>7,36; 14,31</t>
+          <t>7,37; 14,24</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>29,28; 42,34</t>
+          <t>29,32; 43,23</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>25,26; 37,54</t>
+          <t>24,86; 38,09</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>21,04; 32,91</t>
+          <t>21,83; 33,8</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>8,22; 19,8</t>
+          <t>8,16; 20,06</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>24,31; 33,36</t>
+          <t>23,9; 33,0</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>19,92; 28,23</t>
+          <t>20,07; 28,28</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>19,94; 28,32</t>
+          <t>20,23; 28,34</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>8,95; 15,96</t>
+          <t>8,68; 16,12</t>
         </is>
       </c>
     </row>
@@ -1417,62 +1417,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>9,85; 17,25</t>
+          <t>9,56; 17,17</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>14,69; 24,0</t>
+          <t>14,64; 24,46</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>13,22; 22,33</t>
+          <t>13,44; 22,27</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>19,06; 27,69</t>
+          <t>18,85; 27,41</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>27,36; 38,72</t>
+          <t>28,14; 39,59</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>21,85; 32,08</t>
+          <t>21,93; 32,41</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>18,42; 30,15</t>
+          <t>18,66; 29,39</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>23,79; 31,94</t>
+          <t>23,52; 31,5</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>19,84; 27,1</t>
+          <t>19,94; 26,81</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>19,64; 26,72</t>
+          <t>19,41; 26,46</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>17,41; 24,53</t>
+          <t>17,38; 24,23</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>21,92; 27,85</t>
+          <t>22,09; 27,93</t>
         </is>
       </c>
     </row>
@@ -1557,62 +1557,62 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>11,46; 17,05</t>
+          <t>11,3; 16,81</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>12,36; 17,95</t>
+          <t>12,16; 18,06</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>11,69; 17,29</t>
+          <t>11,66; 16,98</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>12,09; 17,87</t>
+          <t>12,04; 17,76</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>25,24; 32,24</t>
+          <t>24,72; 31,97</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>19,88; 26,66</t>
+          <t>20,07; 26,47</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>20,27; 27,19</t>
+          <t>20,65; 27,36</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>9,11; 24,75</t>
+          <t>8,72; 24,93</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>18,73; 23,52</t>
+          <t>19,08; 23,7</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>16,97; 21,38</t>
+          <t>17,08; 21,65</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>16,92; 21,27</t>
+          <t>16,77; 21,36</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>10,07; 19,9</t>
+          <t>10,64; 20,29</t>
         </is>
       </c>
     </row>
@@ -1697,62 +1697,62 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>15,2; 20,57</t>
+          <t>14,84; 20,41</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>10,47; 15,58</t>
+          <t>10,48; 15,45</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>10,01; 14,48</t>
+          <t>10,1; 14,71</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>5,65; 18,99</t>
+          <t>6,13; 19,13</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>22,23; 28,73</t>
+          <t>22,49; 28,72</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>16,19; 21,64</t>
+          <t>16,11; 21,52</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>17,25; 23,42</t>
+          <t>17,51; 23,47</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>23,55; 28,66</t>
+          <t>23,49; 28,55</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>19,49; 23,91</t>
+          <t>19,51; 23,8</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>13,94; 17,68</t>
+          <t>13,9; 17,56</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>14,63; 18,39</t>
+          <t>14,54; 18,34</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>11,59; 22,81</t>
+          <t>11,69; 22,87</t>
         </is>
       </c>
     </row>
@@ -1837,62 +1837,62 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>14,44; 16,89</t>
+          <t>14,38; 16,94</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>15,33; 18,12</t>
+          <t>15,41; 18,1</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>14,37; 16,95</t>
+          <t>14,47; 17,0</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>12,81; 18,25</t>
+          <t>12,65; 18,32</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>26,94; 30,19</t>
+          <t>27,03; 30,22</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>25,08; 28,21</t>
+          <t>25,05; 28,22</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>22,34; 25,42</t>
+          <t>22,44; 25,41</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>17,85; 24,02</t>
+          <t>17,86; 24,01</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>21,21; 23,28</t>
+          <t>21,29; 23,29</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>20,7; 22,78</t>
+          <t>20,88; 22,8</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>18,94; 20,91</t>
+          <t>18,93; 20,81</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>17,03; 20,9</t>
+          <t>16,65; 20,79</t>
         </is>
       </c>
     </row>
@@ -1951,7 +1951,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población con salud general regular o mala</t>
+          <t>Población con salud general regular o mala (tasa de respuesta: 99,93%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -2209,62 +2209,62 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>32496; 56934</t>
+          <t>34122; 58037</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>58516; 90235</t>
+          <t>58895; 90475</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>56801; 87521</t>
+          <t>57284; 88327</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>58791; 90363</t>
+          <t>59509; 90784</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>36423; 62184</t>
+          <t>36462; 60572</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>97880; 132545</t>
+          <t>97032; 132736</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>80637; 114104</t>
+          <t>81056; 113417</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>83144; 111759</t>
+          <t>81991; 111616</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>75226; 111605</t>
+          <t>76191; 110113</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>167649; 211944</t>
+          <t>166875; 212286</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>148205; 190576</t>
+          <t>146707; 189761</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>149133; 192208</t>
+          <t>148794; 192264</t>
         </is>
       </c>
     </row>
@@ -2417,62 +2417,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>69390; 104666</t>
+          <t>70382; 104896</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>71627; 108365</t>
+          <t>71703; 108426</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>57827; 90860</t>
+          <t>58017; 90574</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>60680; 98626</t>
+          <t>59867; 100199</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>139944; 183170</t>
+          <t>142512; 183134</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>141869; 185753</t>
+          <t>142622; 187992</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>98066; 137078</t>
+          <t>99318; 137363</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>80237; 111304</t>
+          <t>81642; 109414</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>220654; 276279</t>
+          <t>221385; 275118</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>220372; 280800</t>
+          <t>224844; 281535</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>165077; 217815</t>
+          <t>166095; 215547</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>148396; 198834</t>
+          <t>146642; 196482</t>
         </is>
       </c>
     </row>
@@ -2625,62 +2625,62 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>34479; 58128</t>
+          <t>35739; 60964</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>39127; 66404</t>
+          <t>39158; 67396</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>31593; 53869</t>
+          <t>31541; 53316</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>48936; 74026</t>
+          <t>49167; 73539</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>91438; 125596</t>
+          <t>93970; 128125</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>64232; 96977</t>
+          <t>65863; 98222</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>41763; 71950</t>
+          <t>43005; 71011</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>66450; 90825</t>
+          <t>65550; 90060</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>133100; 179317</t>
+          <t>133597; 175926</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>111507; 155250</t>
+          <t>111452; 152641</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>81132; 117513</t>
+          <t>81016; 116144</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>122146; 157366</t>
+          <t>120972; 155760</t>
         </is>
       </c>
     </row>
@@ -2833,62 +2833,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>29811; 54671</t>
+          <t>29970; 54172</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>57636; 90784</t>
+          <t>59965; 91081</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>54811; 84976</t>
+          <t>54733; 85657</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>46937; 78455</t>
+          <t>46309; 78512</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>85430; 118102</t>
+          <t>84468; 118606</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>113828; 150992</t>
+          <t>114061; 151925</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>99991; 136581</t>
+          <t>100258; 139094</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>60098; 130347</t>
+          <t>60558; 130471</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>122389; 164880</t>
+          <t>123102; 164090</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>181045; 229299</t>
+          <t>179148; 229196</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>164520; 212132</t>
+          <t>163846; 213918</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>120500; 196050</t>
+          <t>116386; 195168</t>
         </is>
       </c>
     </row>
@@ -3041,62 +3041,62 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>31614; 54922</t>
+          <t>32538; 54282</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>24948; 48079</t>
+          <t>25297; 47886</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>33491; 56849</t>
+          <t>33849; 58399</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>13151; 25571</t>
+          <t>13176; 25445</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>60801; 87936</t>
+          <t>60894; 89775</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>55480; 82437</t>
+          <t>54587; 83644</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>45987; 71932</t>
+          <t>47713; 73886</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>21222; 51129</t>
+          <t>21069; 51801</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>99905; 137093</t>
+          <t>98232; 135620</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>86092; 122033</t>
+          <t>86757; 122225</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>85483; 121442</t>
+          <t>86756; 121532</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>39094; 69731</t>
+          <t>37946; 70454</t>
         </is>
       </c>
     </row>
@@ -3249,62 +3249,62 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>26685; 46703</t>
+          <t>25895; 46485</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>40248; 65765</t>
+          <t>40109; 67005</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>34659; 58536</t>
+          <t>35242; 58385</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>51402; 74669</t>
+          <t>50831; 73919</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>76103; 107698</t>
+          <t>78276; 110109</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>61200; 89843</t>
+          <t>61401; 90755</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>50119; 82016</t>
+          <t>50760; 79939</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>61161; 82097</t>
+          <t>60457; 80968</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>108935; 148762</t>
+          <t>109445; 147166</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>108796; 148044</t>
+          <t>107542; 146584</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>92985; 131013</t>
+          <t>92841; 129417</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>115476; 146688</t>
+          <t>116371; 147127</t>
         </is>
       </c>
     </row>
@@ -3457,62 +3457,62 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>70454; 104875</t>
+          <t>69515; 103383</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>81043; 117738</t>
+          <t>79710; 118462</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>76643; 113379</t>
+          <t>76448; 111335</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>75457; 111532</t>
+          <t>75134; 110901</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>161103; 205755</t>
+          <t>157783; 204051</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>137575; 184466</t>
+          <t>138843; 183181</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>139915; 187653</t>
+          <t>142570; 188850</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>77361; 210200</t>
+          <t>74073; 211748</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>234749; 294758</t>
+          <t>239119; 296966</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>228646; 288152</t>
+          <t>230243; 291753</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>227682; 286262</t>
+          <t>225705; 287540</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>148341; 293164</t>
+          <t>156858; 298999</t>
         </is>
       </c>
     </row>
@@ -3665,62 +3665,62 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>113057; 152993</t>
+          <t>110375; 151795</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>81556; 121378</t>
+          <t>81658; 120345</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>77835; 112562</t>
+          <t>78570; 114409</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>52458; 176370</t>
+          <t>56924; 177671</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>174181; 225078</t>
+          <t>176220; 225029</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>133027; 177830</t>
+          <t>132429; 176873</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>142478; 193456</t>
+          <t>144673; 193940</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>168993; 205725</t>
+          <t>168561; 204916</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>297613; 365245</t>
+          <t>297962; 363549</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>223238; 283041</t>
+          <t>222606; 281152</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>234608; 294929</t>
+          <t>233159; 294187</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
         <is>
-          <t>190840; 375534</t>
+          <t>192468; 376499</t>
         </is>
       </c>
     </row>
@@ -3873,62 +3873,62 @@
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>473016; 553293</t>
+          <t>471042; 554950</t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>524226; 619743</t>
+          <t>527114; 618993</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>486983; 574639</t>
+          <t>490583; 576108</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>443052; 631334</t>
+          <t>437516; 633711</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t>910198; 1020177</t>
+          <t>913456; 1021116</t>
         </is>
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>891178; 1002317</t>
+          <t>890066; 1002703</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>790681; 899567</t>
+          <t>794259; 899176</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
         <is>
-          <t>662368; 891380</t>
+          <t>662805; 891266</t>
         </is>
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>1411771; 1549058</t>
+          <t>1417103; 1550198</t>
         </is>
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>1443221; 1588498</t>
+          <t>1455838; 1589881</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>1312133; 1448582</t>
+          <t>1311433; 1441627</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
         <is>
-          <t>1221613; 1499044</t>
+          <t>1193805; 1491182</t>
         </is>
       </c>
     </row>
